--- a/excel_routes/route_HMB_MED_threats.xlsx
+++ b/excel_routes/route_HMB_MED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6938</v>
+        <v>7068</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11457</v>
+        <v>11578</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4519</v>
+        <v>-4510</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>23</v>
@@ -578,17 +578,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6938</v>
+        <v>7068</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11457</v>
+        <v>11578</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4519</v>
+        <v>-4510</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>23</v>
@@ -623,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6938</v>
+        <v>7068</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11457</v>
+        <v>11578</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4519</v>
+        <v>-4510</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>23</v>
@@ -650,51 +650,6 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-489</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>6938</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>11457</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-4519</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_MED_threats.xlsx
+++ b/excel_routes/route_HMB_MED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7068</v>
+        <v>7016</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4510</v>
+        <v>-4538</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>23</v>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7068</v>
+        <v>7016</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4510</v>
+        <v>-4538</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>23</v>
@@ -605,51 +605,6 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-489</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>7068</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-4510</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_MED_threats.xlsx
+++ b/excel_routes/route_HMB_MED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7016</v>
+        <v>6880</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11554</v>
+        <v>12483</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4538</v>
+        <v>-5603</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>23</v>
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,33 +578,213 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7016</v>
+        <v>8818</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11554</v>
+        <v>12483</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4538</v>
+        <v>-3665</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-489</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>8818</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>12483</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-3665</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-489</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>6880</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>11448</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-4568</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-489</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>9922</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>11448</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-1526</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-489</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>9922</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>11448</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-1526</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
